--- a/premise/data/additional_inventories/lci-carbon-capture.xlsx
+++ b/premise/data/additional_inventories/lci-carbon-capture.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F2CD5-055C-3F46-AA42-8D857D2E85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBB1630-B302-3D4A-8F62-C3184C98C29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="22980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -959,9 +959,6 @@
     <t>carbon dioxide, captured, at cement production plant, using oxyfuel</t>
   </si>
   <si>
-    <t>carbon dioxide, captured and stored, by land-use change</t>
-  </si>
-  <si>
     <t>carbon dioxide, captured and stored, from a hydrogen production plant using steam methane reforming of biomethane</t>
   </si>
   <si>
@@ -1002,6 +999,9 @@
   </si>
   <si>
     <t>For the fermentation-only CCS (FERMCCS) scenario, Dees et al. performed a full material balance to determine the quantity of CO2 capturable from a 40 M-gal (151 ML) per year ethanol plant. Fermentation CO2 is captured at a rate of 13,089 kg/h and assumed to be at 100% purity. Fermentation CO2 is dehydrated, compressed, liquefied, and pumped at 150 bar, which is assumed to be sufficient to transport the gas by pipeline 100 miles to geologic storage without need for further compression. This is carried out by the CO2 processing unit (CPU) and modeled using Aspen Plus V11. The additional electricity demand for the CPU is estimated to be 110 kWh/t CO2 using this model.</t>
+  </si>
+  <si>
+    <t>carbon dioxide, captured and stored, by afforestation</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1138,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1187,8 +1187,6 @@
     <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1899,7 +1897,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B22">
         <v>6.28</v>
@@ -2319,7 +2317,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B44">
         <v>6.28</v>
@@ -5282,7 +5280,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B205">
         <v>5.4</v>
@@ -5618,7 +5616,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B223">
         <v>5.4</v>
@@ -7847,7 +7845,7 @@
       <c r="A345" t="s">
         <v>18</v>
       </c>
-      <c r="B345" s="41" t="s">
+      <c r="B345" t="s">
         <v>221</v>
       </c>
     </row>
@@ -7906,7 +7904,7 @@
       <c r="A349" t="s">
         <v>194</v>
       </c>
-      <c r="B349" s="40">
+      <c r="B349">
         <v>8000</v>
       </c>
       <c r="C349" t="s">
@@ -7929,7 +7927,7 @@
       <c r="A350" t="s">
         <v>103</v>
       </c>
-      <c r="B350" s="40">
+      <c r="B350">
         <v>942000</v>
       </c>
       <c r="C350" t="s">
@@ -7952,7 +7950,7 @@
       <c r="A351" t="s">
         <v>194</v>
       </c>
-      <c r="B351" s="40">
+      <c r="B351">
         <v>6000</v>
       </c>
       <c r="C351" t="s">
@@ -7975,7 +7973,7 @@
       <c r="A352" t="s">
         <v>103</v>
       </c>
-      <c r="B352" s="40">
+      <c r="B352">
         <v>548000.00000000012</v>
       </c>
       <c r="C352" t="s">
@@ -7998,7 +7996,7 @@
       <c r="A353" t="s">
         <v>42</v>
       </c>
-      <c r="B353" s="40">
+      <c r="B353">
         <v>120000</v>
       </c>
       <c r="C353" t="s">
@@ -8021,7 +8019,7 @@
       <c r="A354" t="s">
         <v>115</v>
       </c>
-      <c r="B354" s="40">
+      <c r="B354">
         <v>16000</v>
       </c>
       <c r="C354" t="s">
@@ -8044,7 +8042,7 @@
       <c r="A355" t="s">
         <v>59</v>
       </c>
-      <c r="B355" s="40">
+      <c r="B355">
         <v>276000.00000000006</v>
       </c>
       <c r="C355" t="s">
@@ -8067,7 +8065,7 @@
       <c r="A356" t="s">
         <v>43</v>
       </c>
-      <c r="B356" s="40">
+      <c r="B356">
         <v>224000</v>
       </c>
       <c r="C356" t="s">
@@ -8090,7 +8088,7 @@
       <c r="A357" t="s">
         <v>115</v>
       </c>
-      <c r="B357" s="40">
+      <c r="B357">
         <v>10000</v>
       </c>
       <c r="C357" t="s">
@@ -8113,7 +8111,7 @@
       <c r="A358" t="s">
         <v>116</v>
       </c>
-      <c r="B358" s="40">
+      <c r="B358">
         <v>12000</v>
       </c>
       <c r="C358" t="s">
@@ -8136,7 +8134,7 @@
       <c r="A359" t="s">
         <v>152</v>
       </c>
-      <c r="B359" s="40">
+      <c r="B359">
         <v>10000</v>
       </c>
       <c r="C359" t="s">
@@ -8159,7 +8157,7 @@
       <c r="A360" t="s">
         <v>58</v>
       </c>
-      <c r="B360" s="40">
+      <c r="B360">
         <v>160000</v>
       </c>
       <c r="C360" t="s">
@@ -8182,7 +8180,7 @@
       <c r="A361" t="s">
         <v>117</v>
       </c>
-      <c r="B361" s="40">
+      <c r="B361">
         <v>10000</v>
       </c>
       <c r="C361" t="s">
@@ -8205,7 +8203,7 @@
       <c r="A362" t="s">
         <v>43</v>
       </c>
-      <c r="B362" s="40">
+      <c r="B362">
         <v>338000</v>
       </c>
       <c r="C362" t="s">
@@ -8228,7 +8226,7 @@
       <c r="A363" t="s">
         <v>42</v>
       </c>
-      <c r="B363" s="40">
+      <c r="B363">
         <v>28000</v>
       </c>
       <c r="C363" t="s">
@@ -8251,7 +8249,7 @@
       <c r="A364" t="s">
         <v>121</v>
       </c>
-      <c r="B364" s="40">
+      <c r="B364">
         <v>94000</v>
       </c>
       <c r="C364" t="s">
@@ -8274,7 +8272,7 @@
       <c r="A365" t="s">
         <v>116</v>
       </c>
-      <c r="B365" s="40">
+      <c r="B365">
         <v>10000</v>
       </c>
       <c r="C365" t="s">
@@ -8297,7 +8295,7 @@
       <c r="A366" t="s">
         <v>152</v>
       </c>
-      <c r="B366" s="40">
+      <c r="B366">
         <v>10000</v>
       </c>
       <c r="C366" t="s">
@@ -8320,7 +8318,7 @@
       <c r="A367" t="s">
         <v>43</v>
       </c>
-      <c r="B367" s="40">
+      <c r="B367">
         <v>22000</v>
       </c>
       <c r="C367" t="s">
@@ -8343,7 +8341,7 @@
       <c r="A368" t="s">
         <v>42</v>
       </c>
-      <c r="B368" s="40">
+      <c r="B368">
         <v>12000</v>
       </c>
       <c r="C368" t="s">
@@ -11714,7 +11712,7 @@
     </row>
     <row r="540" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B540" s="29">
         <f>(3.76-0.11)/0.9</f>
@@ -12355,7 +12353,7 @@
         <v>0</v>
       </c>
       <c r="B582" s="34" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
     </row>
     <row r="583" spans="1:22" x14ac:dyDescent="0.2">
@@ -12437,7 +12435,7 @@
     <row r="589" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A589" t="str">
         <f>B582</f>
-        <v>carbon dioxide, captured and stored, by land-use change</v>
+        <v>carbon dioxide, captured and stored, by afforestation</v>
       </c>
       <c r="B589" s="35">
         <v>1</v>
@@ -13137,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="623" spans="1:17" x14ac:dyDescent="0.2">
@@ -13185,7 +13183,7 @@
         <v>18</v>
       </c>
       <c r="B628" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="629" spans="1:13" x14ac:dyDescent="0.2">
@@ -13193,7 +13191,7 @@
         <v>9</v>
       </c>
       <c r="B629" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="630" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -13284,7 +13282,7 @@
         <v>24</v>
       </c>
       <c r="H633" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I633">
         <v>5</v>
@@ -13321,7 +13319,7 @@
         <v>32</v>
       </c>
       <c r="H634" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I634">
         <v>5</v>
@@ -13358,7 +13356,7 @@
         <v>24</v>
       </c>
       <c r="H635" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I635">
         <v>5</v>
@@ -13394,7 +13392,7 @@
         <v>141</v>
       </c>
       <c r="H636" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I636">
         <v>5</v>
@@ -13431,7 +13429,7 @@
         <v>24</v>
       </c>
       <c r="H637" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I637">
         <v>5</v>
@@ -13467,7 +13465,7 @@
         <v>30</v>
       </c>
       <c r="H638" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="639" spans="1:13" x14ac:dyDescent="0.2">
@@ -13490,7 +13488,7 @@
         <v>50</v>
       </c>
       <c r="H639" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="640" spans="1:13" x14ac:dyDescent="0.2">
@@ -13568,7 +13566,7 @@
         <v>0</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="645" spans="1:13" x14ac:dyDescent="0.2">
@@ -13616,7 +13614,7 @@
         <v>18</v>
       </c>
       <c r="B650" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="651" spans="1:13" x14ac:dyDescent="0.2">
@@ -13624,7 +13622,7 @@
         <v>9</v>
       </c>
       <c r="B651" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="652" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -13714,7 +13712,7 @@
         <v>24</v>
       </c>
       <c r="H655" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I655">
         <v>5</v>
